--- a/dcf/SCCO.xlsx
+++ b/dcf/SCCO.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1139,25 +1139,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.08669660422787308</v>
+        <v>0.08667605220955785</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.09169660422787308</v>
+        <v>0.09167605220955785</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.09669660422787307</v>
+        <v>0.09667605220955784</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1016966042278731</v>
+        <v>0.1016760522095578</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1066966042278731</v>
+        <v>0.1066760522095579</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1116966042278731</v>
+        <v>0.1116760522095578</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1166966042278731</v>
+        <v>0.1166760522095578</v>
       </c>
     </row>
     <row r="5">
@@ -1165,25 +1165,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>74.2667854613541</v>
+        <v>74.27778057550641</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>71.65263564594601</v>
+        <v>71.66313730174419</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>69.15543132903852</v>
+        <v>69.16546471044599</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>66.76921991646918</v>
+        <v>66.77880879522655</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>64.48838180187589</v>
+        <v>64.49754862320231</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>62.30761020637564</v>
+        <v>62.31637616909173</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>60.22189232727337</v>
+        <v>60.23027745873421</v>
       </c>
     </row>
     <row r="6">
@@ -1191,25 +1191,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>78.81334553131795</v>
+        <v>78.82520059760184</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>75.99520175677164</v>
+        <v>76.00652101829959</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>73.3040263864555</v>
+        <v>73.31483729183684</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>70.7333319952005</v>
+        <v>70.74366045020219</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>68.276994925617</v>
+        <v>68.28686538694249</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>65.92923322853274</v>
+        <v>65.93866879148948</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>63.68458603746911</v>
+        <v>63.69360851795052</v>
       </c>
     </row>
     <row r="7">
@@ -1217,25 +1217,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>83.35990560128181</v>
+        <v>83.37262061969726</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>80.33776786759725</v>
+        <v>80.34990473485499</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>77.45262144387247</v>
+        <v>77.46420987322767</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>74.69744407393182</v>
+        <v>74.70851210517782</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>72.06560804935809</v>
+        <v>72.07618215068268</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>69.55085625068983</v>
+        <v>69.56096141388723</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>67.14727974766484</v>
+        <v>67.15693957716682</v>
       </c>
     </row>
     <row r="8">
@@ -1243,25 +1243,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>87.90646567124567</v>
+        <v>87.92004064179268</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>84.68033397842287</v>
+        <v>84.69328845141038</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>81.60121650128946</v>
+        <v>81.61358245461852</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>78.66155615266312</v>
+        <v>78.67336376015344</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>75.85422117309919</v>
+        <v>75.86549891442287</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>73.17247927284691</v>
+        <v>73.18325403628498</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>70.60997345786058</v>
+        <v>70.62027063638311</v>
       </c>
     </row>
     <row r="9">
@@ -1269,25 +1269,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>92.45302574120953</v>
+        <v>92.4674606638881</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>89.02290008924847</v>
+        <v>89.03667216796578</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>85.74981155870644</v>
+        <v>85.76295503600936</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>82.62566823139444</v>
+        <v>82.63821541512908</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>79.64283429684031</v>
+        <v>79.65481567816308</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>76.79410229500402</v>
+        <v>76.8055466586827</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>74.07266716805631</v>
+        <v>74.08360169559943</v>
       </c>
     </row>
     <row r="10">
@@ -1295,25 +1295,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>96.99958581117336</v>
+        <v>97.01488068598353</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>93.3654662000741</v>
+        <v>93.38005588452118</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>89.89840661612344</v>
+        <v>89.91232761740021</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>86.58978031012575</v>
+        <v>86.60306707010471</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>83.43144742058142</v>
+        <v>83.44413244190326</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>80.41572531716113</v>
+        <v>80.42783928108048</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>77.53536087825206</v>
+        <v>77.54693275481574</v>
       </c>
     </row>
     <row r="11">
@@ -1321,25 +1321,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>101.5461458811372</v>
+        <v>101.562300708079</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>97.70803231089971</v>
+        <v>97.72343960107658</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>94.04700167354042</v>
+        <v>94.06170019879106</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>90.55389238885708</v>
+        <v>90.56791872508035</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>87.22006054432252</v>
+        <v>87.23344920564345</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>84.03734833931823</v>
+        <v>84.0501319034782</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>80.9980545884478</v>
+        <v>81.01026381403204</v>
       </c>
     </row>
     <row r="13">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>172.0099945068359</v>
+        <v>170.8684997558594</v>
       </c>
     </row>
     <row r="14">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1016966042278731</v>
+        <v>0.1016760522095578</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9393072594490172</v>
+        <v>0.9393106411895232</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24508,7 +24508,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>172.0099945068359</v>
+        <v>170.8684997558594</v>
       </c>
     </row>
     <row r="49">
@@ -24670,13 +24670,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>78.66155615266312</v>
+        <v>78.67336376015344</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>107.4364266190442</v>
+        <v>107.4531702394937</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>57.07434784711394</v>
+        <v>57.08251329667306</v>
       </c>
     </row>
     <row r="59">
